--- a/business_forms/036_it_service_ticket_form--business_forms.xlsx
+++ b/business_forms/036_it_service_ticket_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>submit_ticket</t>
+          <t>issue_description</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>submit_ticket</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the issue?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Briefly describe the issue</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>issue_description_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Description of the issue</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Provide more details about the issue</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>is_priority</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Is this a priority issue?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Check if this issue requires immediate attention</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,18 +601,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>priority_type</t>
+          <t>category_select</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>priority_type</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Select all relevant categories for the issue</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Choose all categories that apply</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>assignee</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Who reported the issue?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter the name of the person who reported the issue</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,66 +650,78 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>category_type</t>
+          <t>due_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>category_type</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is the due date for the issue?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter the due date for the issue</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>assignee</t>
+          <t>reporter_email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>assignee</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is the email address of the reporter?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter the email address of the reporter</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>due_date</t>
+          <t>reporter_phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>due_date</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is the phone number of the reporter?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter the phone number of the reporter</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>submitter</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>submitter</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Comments for the reporter</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Any comments from the reporter</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>submitter_type</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>submitter_type</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Is the reporter available for follow-up?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Check if the reporter is available for follow-up</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>submitter_email</t>
+          <t>submitter_type</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>submitter_email</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>How will the issue be submitted?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Choose the method of submission</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>submitter_phone</t>
+          <t>submitter_method</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>submitter_phone</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is the type of the submitter?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Check if the submitter is individual or department</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>description_text</t>
+          <t>contact_method</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>How would you like to be contacted?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Choose a contact method</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,20 +866,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>is_urgent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Is this an urgent issue?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Check if this issue is urgent</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submitter</t>
+          <t>is_escalate</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>submitter</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Is this issue that requires escalation?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Check if this issue requires escalation</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -865,85 +925,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>submitter_type</t>
+          <t>follow_up_from_submitter</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>submitter_type</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Is this issue that requires follow-up from the submitter?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Check if this issue requires follow-up from the submitter</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>submitter_email</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>submitter_email</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>submitter_phone</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>submitter_phone</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -960,12 +955,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -988,204 +983,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>priority_choices</t>
+          <t>is_priority_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>priority_choices</t>
+          <t>is_priority_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>priority_type_choices</t>
+          <t>category_select_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>priority_type_choices</t>
+          <t>category_select_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_select_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assignee_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>John</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>category_type_choices</t>
+          <t>assignee_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>category_type_choices</t>
+          <t>assignee_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>assignee_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>assignee_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>submitter_choices</t>
+          <t>submitter_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>submitter_choices</t>
+          <t>submitter_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1197,97 +1192,148 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>submitter_type_choices</t>
+          <t>submitter_method_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>submitter_choices</t>
+          <t>submitter_method_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Department</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>submitter_choices</t>
+          <t>is_urgent_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>submitter_type_choices</t>
+          <t>is_urgent_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>submitter_type_choices</t>
+          <t>is_escalate_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>is_escalate_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>follow_up_from_submitter_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>follow_up_from_submitter_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
